--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/2388-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/2388-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{551C6E34-F629-4F3E-9D1D-169E3BB31728}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8940583F-BD61-4946-8C92-444F197675DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{4AB22DF9-CC2A-4ABA-BAC6-40A41E5F9755}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{B057117C-27E7-4FF9-B5F6-8A6C2DAEB9F4}"/>
   </bookViews>
   <sheets>
     <sheet name="2388-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1445,28 +1445,27 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC0075DC-DB2A-4C3C-A248-DAD55396EF68}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A02969D-6378-4461-BC11-691CD2001457}">
   <dimension ref="A1:X38"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="11.375" customWidth="1"/>
-    <col min="3" max="3" width="10.25" customWidth="1"/>
-    <col min="4" max="6" width="6.25" customWidth="1"/>
-    <col min="7" max="7" width="6.625" customWidth="1"/>
-    <col min="8" max="8" width="6.25" customWidth="1"/>
-    <col min="9" max="10" width="6.625" customWidth="1"/>
-    <col min="11" max="13" width="6.25" customWidth="1"/>
-    <col min="14" max="14" width="6.625" customWidth="1"/>
-    <col min="15" max="18" width="6.25" customWidth="1"/>
-    <col min="19" max="19" width="6.625" customWidth="1"/>
-    <col min="20" max="20" width="6.25" customWidth="1"/>
-    <col min="21" max="21" width="6.625" customWidth="1"/>
-    <col min="22" max="22" width="6.25" customWidth="1"/>
-    <col min="23" max="23" width="6.625" customWidth="1"/>
-    <col min="24" max="24" width="8.25" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="15" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
@@ -1500,7 +1499,7 @@
       <c r="W1" s="27"/>
       <c r="X1" s="19"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
@@ -1536,7 +1535,7 @@
       <c r="W2" s="29"/>
       <c r="X2" s="30"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="20" t="s">
         <v>2</v>
       </c>
@@ -1588,7 +1587,7 @@
       </c>
       <c r="X3" s="33"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="22"/>
       <c r="B4" s="23"/>
       <c r="C4" s="7"/>
@@ -1656,7 +1655,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="34">
         <v>2024</v>
       </c>
@@ -1728,7 +1727,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="36">
         <v>2023</v>
       </c>
@@ -1800,7 +1799,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="34">
         <v>2022</v>
       </c>
@@ -1872,7 +1871,7 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="36">
         <v>2021</v>
       </c>
@@ -1944,7 +1943,7 @@
         <v>2.35</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="34">
         <v>2020</v>
       </c>
@@ -2016,7 +2015,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="36">
         <v>2019</v>
       </c>
@@ -2088,7 +2087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="34">
         <v>2018</v>
       </c>
@@ -2160,7 +2159,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="36">
         <v>2017</v>
       </c>
@@ -2232,7 +2231,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="34">
         <v>2016</v>
       </c>
@@ -2304,7 +2303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="36">
         <v>2015</v>
       </c>
@@ -2376,7 +2375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="34">
         <v>2014</v>
       </c>
@@ -2448,7 +2447,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="36">
         <v>2013</v>
       </c>
@@ -2520,7 +2519,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="34">
         <v>2012</v>
       </c>
@@ -2592,7 +2591,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="36">
         <v>2011</v>
       </c>
@@ -2664,7 +2663,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="34">
         <v>2010</v>
       </c>
@@ -2736,7 +2735,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="36">
         <v>2009</v>
       </c>
@@ -2808,7 +2807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="34">
         <v>2008</v>
       </c>
@@ -2880,7 +2879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="36">
         <v>2007</v>
       </c>
@@ -2952,7 +2951,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="34">
         <v>2006</v>
       </c>
@@ -3024,7 +3023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="36">
         <v>2005</v>
       </c>
@@ -3096,7 +3095,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="34">
         <v>2004</v>
       </c>
@@ -3168,7 +3167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="36">
         <v>2003</v>
       </c>
@@ -3240,7 +3239,7 @@
         <v>3.47</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="34">
         <v>2002</v>
       </c>
@@ -3312,7 +3311,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="36">
         <v>2001</v>
       </c>
@@ -3384,7 +3383,7 @@
         <v>8.4499999999999993</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="34">
         <v>2000</v>
       </c>
@@ -3456,7 +3455,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="36">
         <v>1999</v>
       </c>
@@ -3528,7 +3527,7 @@
         <v>3.03</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="34">
         <v>1998</v>
       </c>
@@ -3600,7 +3599,7 @@
         <v>4.6900000000000004</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="36">
         <v>1997</v>
       </c>
@@ -3672,7 +3671,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="34">
         <v>1996</v>
       </c>
@@ -3744,7 +3743,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="36">
         <v>1995</v>
       </c>
@@ -3816,7 +3815,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="34">
         <v>1994</v>
       </c>
@@ -3888,7 +3887,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="36">
         <v>1993</v>
       </c>
@@ -3960,7 +3959,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="34">
         <v>1992</v>
       </c>
@@ -4032,7 +4031,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="36" t="s">
         <v>40</v>
       </c>
